--- a/Dados/Bruto/PIB mesos.xlsx
+++ b/Dados/Bruto/PIB mesos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao-giorio\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao-giorio\Desktop\Painel PIB Municípios\Dados\Bruto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24818D06-2464-4BB8-A298-13D2406A8956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0721EEC4-0CDC-41FA-A97C-FC2259752874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="4455" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Mesos</t>
-  </si>
-  <si>
     <t>Grande Florianópolis</t>
   </si>
   <si>
@@ -61,23 +58,15 @@
   <si>
     <t>Santa Catarina</t>
   </si>
+  <si>
+    <t>Mesorregião</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,7 +91,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -112,12 +101,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -133,6 +116,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B084"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -143,26 +138,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -444,104 +442,132 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="30" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1">
         <v>2002</v>
       </c>
       <c r="C1" s="1">
+        <f>B1+1</f>
         <v>2003</v>
       </c>
       <c r="D1" s="1">
+        <f>C1+1</f>
         <v>2004</v>
       </c>
       <c r="E1" s="1">
+        <f t="shared" ref="E1:AD1" si="0">D1+1</f>
         <v>2005</v>
       </c>
       <c r="F1" s="1">
+        <f t="shared" si="0"/>
         <v>2006</v>
       </c>
       <c r="G1" s="1">
+        <f t="shared" si="0"/>
         <v>2007</v>
       </c>
       <c r="H1" s="1">
+        <f t="shared" si="0"/>
         <v>2008</v>
       </c>
       <c r="I1" s="1">
+        <f t="shared" si="0"/>
         <v>2009</v>
       </c>
       <c r="J1" s="1">
+        <f t="shared" si="0"/>
         <v>2010</v>
       </c>
       <c r="K1" s="1">
+        <f t="shared" si="0"/>
         <v>2011</v>
       </c>
       <c r="L1" s="1">
+        <f t="shared" si="0"/>
         <v>2012</v>
       </c>
       <c r="M1" s="1">
+        <f t="shared" si="0"/>
         <v>2013</v>
       </c>
       <c r="N1" s="1">
+        <f t="shared" si="0"/>
         <v>2014</v>
       </c>
       <c r="O1" s="1">
+        <f t="shared" si="0"/>
         <v>2015</v>
       </c>
       <c r="P1" s="1">
+        <f t="shared" si="0"/>
         <v>2016</v>
       </c>
       <c r="Q1" s="1">
+        <f t="shared" si="0"/>
         <v>2017</v>
       </c>
       <c r="R1" s="1">
+        <f t="shared" si="0"/>
         <v>2018</v>
       </c>
       <c r="S1" s="1">
+        <f t="shared" si="0"/>
         <v>2019</v>
       </c>
       <c r="T1" s="1">
+        <f t="shared" si="0"/>
         <v>2020</v>
       </c>
       <c r="U1" s="1">
+        <f t="shared" si="0"/>
         <v>2021</v>
       </c>
       <c r="V1" s="1">
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
       <c r="W1" s="1">
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="X1" s="1">
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="Y1" s="1">
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
       <c r="Z1" s="1">
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
       <c r="AA1" s="1">
+        <f t="shared" si="0"/>
         <v>2027</v>
       </c>
       <c r="AB1" s="1">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="AC1" s="1">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="AD1" s="1">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>44641161659</v>
@@ -592,13 +618,13 @@
         <v>66245294412</v>
       </c>
       <c r="R2" s="3">
+        <v>71436460357</v>
+      </c>
+      <c r="S2" s="3">
+        <v>65374496885</v>
+      </c>
+      <c r="T2" s="3">
         <v>70006242669</v>
-      </c>
-      <c r="S2" s="3">
-        <v>71436460357</v>
-      </c>
-      <c r="T2" s="3">
-        <v>65374496885</v>
       </c>
       <c r="U2" s="3">
         <v>67093153395</v>
@@ -627,13 +653,13 @@
       <c r="AC2" s="4">
         <v>85349833713.25853</v>
       </c>
-      <c r="AD2" s="4">
+      <c r="AD2" s="5">
         <v>87478400339.95929</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>71679771479</v>
@@ -684,13 +710,13 @@
         <v>96180533760</v>
       </c>
       <c r="R3" s="3">
+        <v>107341730822</v>
+      </c>
+      <c r="S3" s="3">
+        <v>104365088580</v>
+      </c>
+      <c r="T3" s="3">
         <v>102531493875</v>
-      </c>
-      <c r="S3" s="3">
-        <v>107341730822</v>
-      </c>
-      <c r="T3" s="3">
-        <v>104365088580</v>
       </c>
       <c r="U3" s="3">
         <v>118002797584</v>
@@ -699,33 +725,33 @@
         <v>114463852329.56001</v>
       </c>
       <c r="W3" s="3">
-        <v>116874219330.4287</v>
+        <v>114991451000</v>
       </c>
       <c r="X3" s="4">
-        <v>124669407488.40097</v>
+        <v>122576918236.40192</v>
       </c>
       <c r="Y3" s="4">
-        <v>128658497292.75339</v>
+        <v>126439673448.25826</v>
       </c>
       <c r="Z3" s="4">
-        <v>130946475692.6546</v>
+        <v>128640304883.78075</v>
       </c>
       <c r="AA3" s="4">
-        <v>135816984725.84485</v>
+        <v>133350782716.4825</v>
       </c>
       <c r="AB3" s="4">
-        <v>141700467909.81082</v>
+        <v>139039234660.66104</v>
       </c>
       <c r="AC3" s="4">
-        <v>147517584346.5835</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>153464871902.6181</v>
+        <v>144655418604.49319</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>150391143565.14072</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>58386888974</v>
@@ -776,13 +802,13 @@
         <v>73167778120</v>
       </c>
       <c r="R4" s="3">
+        <v>79063235287</v>
+      </c>
+      <c r="S4" s="3">
+        <v>80360725581</v>
+      </c>
+      <c r="T4" s="3">
         <v>75923521052</v>
-      </c>
-      <c r="S4" s="3">
-        <v>79063235287</v>
-      </c>
-      <c r="T4" s="3">
-        <v>80360725581</v>
       </c>
       <c r="U4" s="3">
         <v>83015777557</v>
@@ -811,13 +837,13 @@
       <c r="AC4" s="4">
         <v>101408343758.74751</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AD4" s="5">
         <v>103554377558.09004</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>17997328376</v>
@@ -868,13 +894,13 @@
         <v>23086796797</v>
       </c>
       <c r="R5" s="3">
+        <v>23901696867</v>
+      </c>
+      <c r="S5" s="3">
+        <v>23181013511</v>
+      </c>
+      <c r="T5" s="3">
         <v>22744281327</v>
-      </c>
-      <c r="S5" s="3">
-        <v>23901696867</v>
-      </c>
-      <c r="T5" s="3">
-        <v>23181013511</v>
       </c>
       <c r="U5" s="3">
         <v>23855260102</v>
@@ -903,13 +929,13 @@
       <c r="AC5" s="4">
         <v>27712963292.746319</v>
       </c>
-      <c r="AD5" s="4">
+      <c r="AD5" s="5">
         <v>28201029987.034966</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>35657704239</v>
@@ -960,13 +986,13 @@
         <v>49116360426</v>
       </c>
       <c r="R6" s="3">
+        <v>52491251277</v>
+      </c>
+      <c r="S6" s="3">
+        <v>51502385409</v>
+      </c>
+      <c r="T6" s="3">
         <v>51206202427</v>
-      </c>
-      <c r="S6" s="3">
-        <v>52491251277</v>
-      </c>
-      <c r="T6" s="3">
-        <v>51502385409</v>
       </c>
       <c r="U6" s="3">
         <v>53646517430</v>
@@ -978,30 +1004,30 @@
         <v>56433884000</v>
       </c>
       <c r="X6" s="4">
-        <v>58679646215.231873</v>
+        <v>58666946745.582291</v>
       </c>
       <c r="Y6" s="4">
-        <v>59973562615.988182</v>
+        <v>59952209180.838905</v>
       </c>
       <c r="Z6" s="4">
-        <v>60837654475.179367</v>
+        <v>60809516138.874687</v>
       </c>
       <c r="AA6" s="4">
-        <v>62289561271.094879</v>
+        <v>62250591963.849091</v>
       </c>
       <c r="AB6" s="4">
-        <v>63945087976.885201</v>
+        <v>63893197248.355186</v>
       </c>
       <c r="AC6" s="4">
-        <v>65540229652.35498</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>67115240061.296181</v>
+        <v>65474841377.204498</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>67035510133.508476</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>74062280288</v>
@@ -1052,13 +1078,13 @@
         <v>131325619198</v>
       </c>
       <c r="R7" s="3">
+        <v>143895644669</v>
+      </c>
+      <c r="S7" s="3">
+        <v>141326271371</v>
+      </c>
+      <c r="T7" s="3">
         <v>138637853687</v>
-      </c>
-      <c r="S7" s="3">
-        <v>143895644669</v>
-      </c>
-      <c r="T7" s="3">
-        <v>141326271371</v>
       </c>
       <c r="U7" s="3">
         <v>160221432719</v>
@@ -1067,149 +1093,120 @@
         <v>162554872792.59998</v>
       </c>
       <c r="W7" s="3">
-        <v>167593747964.7804</v>
+        <v>155681928000</v>
       </c>
       <c r="X7" s="4">
-        <v>181657069636.19006</v>
+        <v>168357815291.69296</v>
       </c>
       <c r="Y7" s="4">
-        <v>190171801743.00131</v>
+        <v>175902142141.15759</v>
       </c>
       <c r="Z7" s="4">
-        <v>196047464966.02933</v>
+        <v>180967216163.34741</v>
       </c>
       <c r="AA7" s="4">
-        <v>206075779408.18491</v>
+        <v>189787392907.68164</v>
       </c>
       <c r="AB7" s="4">
-        <v>217879299179.01233</v>
+        <v>200171732797.59818</v>
       </c>
       <c r="AC7" s="4">
-        <v>229652437061.05823</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>241659884237.19629</v>
+        <v>210455241369.6991</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>220872826150.09607</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5">
-        <f t="shared" ref="B8:AD8" si="0">SUM(B2:B7)</f>
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
         <v>302425135015</v>
       </c>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
+      <c r="C8" s="3">
         <v>310558754291</v>
       </c>
-      <c r="D8" s="5">
-        <f t="shared" si="0"/>
+      <c r="D8" s="3">
         <v>331005528845</v>
       </c>
-      <c r="E8" s="5">
-        <f t="shared" si="0"/>
+      <c r="E8" s="3">
         <v>341992660193</v>
       </c>
-      <c r="F8" s="5">
-        <f t="shared" si="0"/>
+      <c r="F8" s="3">
         <v>348651317761</v>
       </c>
-      <c r="G8" s="5">
-        <f t="shared" si="0"/>
+      <c r="G8" s="3">
         <v>369958948008</v>
       </c>
-      <c r="H8" s="5">
-        <f t="shared" si="0"/>
+      <c r="H8" s="3">
         <v>377545563454</v>
       </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
+      <c r="I8" s="3">
         <v>374349220884</v>
       </c>
-      <c r="J8" s="5">
-        <f t="shared" si="0"/>
+      <c r="J8" s="3">
         <v>399481458027</v>
       </c>
-      <c r="K8" s="5">
-        <f t="shared" si="0"/>
+      <c r="K8" s="3">
         <v>414992864205</v>
       </c>
-      <c r="L8" s="5">
-        <f t="shared" si="0"/>
+      <c r="L8" s="3">
         <v>420574532563</v>
       </c>
-      <c r="M8" s="5">
-        <f t="shared" si="0"/>
+      <c r="M8" s="3">
         <v>435779698481</v>
       </c>
-      <c r="N8" s="5">
-        <f t="shared" si="0"/>
+      <c r="N8" s="3">
         <v>445572342640</v>
       </c>
-      <c r="O8" s="5">
-        <f t="shared" si="0"/>
+      <c r="O8" s="3">
         <v>430296409395</v>
       </c>
-      <c r="P8" s="5">
-        <f t="shared" si="0"/>
+      <c r="P8" s="3">
         <v>421306597311</v>
       </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="0"/>
+      <c r="Q8" s="3">
         <v>439122382713</v>
       </c>
-      <c r="R8" s="5">
-        <f t="shared" si="0"/>
+      <c r="R8" s="3">
+        <v>478130019279</v>
+      </c>
+      <c r="S8" s="3">
+        <v>466109981337</v>
+      </c>
+      <c r="T8" s="3">
         <v>461049595037</v>
       </c>
-      <c r="S8" s="5">
-        <f t="shared" si="0"/>
-        <v>478130019279</v>
-      </c>
-      <c r="T8" s="5">
-        <f t="shared" si="0"/>
-        <v>466109981337</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" si="0"/>
+      <c r="U8" s="3">
         <v>505834938787</v>
       </c>
-      <c r="V8" s="5">
-        <f t="shared" si="0"/>
+      <c r="V8" s="3">
         <v>510853581829.51001</v>
       </c>
-      <c r="W8" s="5">
-        <f t="shared" si="0"/>
-        <v>527187560295.20911</v>
+      <c r="W8" s="3">
+        <v>513392972000</v>
       </c>
       <c r="X8" s="4">
-        <f t="shared" si="0"/>
-        <v>558906394419.1665</v>
+        <v>543501951353.02075</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" si="0"/>
-        <v>576597286126.8092</v>
+        <v>560087449245.32117</v>
       </c>
       <c r="Z8" s="4">
-        <f t="shared" si="0"/>
-        <v>587827429378.01221</v>
+        <v>570412871430.15173</v>
       </c>
       <c r="AA8" s="4">
-        <f t="shared" si="0"/>
-        <v>608602144157.75439</v>
+        <v>589808586340.64294</v>
       </c>
       <c r="AB8" s="4">
-        <f t="shared" si="0"/>
-        <v>633109280042.09424</v>
+        <v>612688589683.00037</v>
       </c>
       <c r="AC8" s="4">
-        <f t="shared" si="0"/>
-        <v>657181391824.74902</v>
-      </c>
-      <c r="AD8" s="4">
-        <f t="shared" si="0"/>
-        <v>681473804086.19482</v>
+        <v>635056642116.14917</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>657533287733.82959</v>
       </c>
     </row>
   </sheetData>
